--- a/_data/PLCTags_FG01.xlsx
+++ b/_data/PLCTags_FG01.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R388401ef71d64693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R4e5e608786834c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R5257cfb07e4a4193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R2ccacdd262244f15"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
   <x:si>
     <x:t xml:space="preserve">Name</x:t>
   </x:si>
@@ -53,73 +53,91 @@
     <x:t xml:space="preserve">%I101.0</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">geöffnet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">True</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"/>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Gripper_InWork</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I101.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">geschlossen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Gripper_WorkPos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q101.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">schließen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Plattform_InHome</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I102.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hinten</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Plattform_InWork</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I102.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vorne</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Plattform_HomePos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q102.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Plattform_WorkPos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q102.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_ReaderWindow_InWork</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I103.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_ReaderWindow_WorkPos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q103.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Position zum Code Lesen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG01_Y_Gripper_HomePos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q101.0</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">öffnen</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">True</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"/>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_Gripper_InWork</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%I101.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">schließen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_Gripper_WorkPos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q101.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_Plattform_InHome</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%I102.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">hinten</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_Plattform_InWork</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%I102.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">vorne</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_Plattform_HomePos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q102.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_Plattform_WorkPos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q102.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_ReaderWindow_InWork</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%I103.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FG01_Y_ReaderWindow_WorkPos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q103.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Position zum Code Lesen</x:t>
+    <x:t xml:space="preserve">FG01_Y_ReaderWindow_HomePos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q103.0</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BelongsToUnit</x:t>
@@ -289,7 +307,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
@@ -309,7 +327,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>11</x:v>
@@ -318,10 +336,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>15</x:v>
@@ -341,7 +359,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>11</x:v>
@@ -350,10 +368,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>15</x:v>
@@ -373,7 +391,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>11</x:v>
@@ -382,7 +400,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>16</x:v>
@@ -405,7 +423,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>11</x:v>
@@ -414,7 +432,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>16</x:v>
@@ -437,7 +455,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>11</x:v>
@@ -446,7 +464,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>16</x:v>
@@ -469,7 +487,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>11</x:v>
@@ -478,10 +496,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>15</x:v>
@@ -496,6 +514,70 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -511,10 +593,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
